--- a/Team-Data/2014-15/1-18-2014-15.xlsx
+++ b/Team-Data/2014-15/1-18-2014-15.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -775,7 +842,7 @@
         <v>12</v>
       </c>
       <c r="AP2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ2" t="n">
         <v>9</v>
@@ -793,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
         <v>5</v>
@@ -802,7 +869,7 @@
         <v>15</v>
       </c>
       <c r="AY2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ2" t="n">
         <v>1</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -930,7 +997,7 @@
         <v>21</v>
       </c>
       <c r="AG3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH3" t="n">
         <v>6</v>
@@ -942,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL3" t="n">
         <v>14</v>
@@ -960,7 +1027,7 @@
         <v>27</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
         <v>17</v>
@@ -975,7 +1042,7 @@
         <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW3" t="n">
         <v>10</v>
@@ -984,10 +1051,10 @@
         <v>24</v>
       </c>
       <c r="AY3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA3" t="n">
         <v>30</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1182,7 @@
         <v>19</v>
       </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI4" t="n">
         <v>25</v>
@@ -1154,13 +1221,13 @@
         <v>20</v>
       </c>
       <c r="AU4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX4" t="n">
         <v>25</v>
@@ -1172,10 +1239,10 @@
         <v>14</v>
       </c>
       <c r="BA4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC4" t="n">
         <v>22</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -1303,7 +1370,7 @@
         <v>24</v>
       </c>
       <c r="AJ5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK5" t="n">
         <v>28</v>
@@ -1333,7 +1400,7 @@
         <v>9</v>
       </c>
       <c r="AT5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU5" t="n">
         <v>29</v>
@@ -1357,7 +1424,7 @@
         <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC5" t="n">
         <v>23</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1537,7 @@
         <v>2</v>
       </c>
       <c r="AE6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF6" t="n">
         <v>10</v>
@@ -1539,7 +1606,7 @@
         <v>2</v>
       </c>
       <c r="BB6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -1670,7 +1737,7 @@
         <v>21</v>
       </c>
       <c r="AK7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL7" t="n">
         <v>10</v>
@@ -1685,10 +1752,10 @@
         <v>6</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR7" t="n">
         <v>14</v>
@@ -1706,13 +1773,13 @@
         <v>10</v>
       </c>
       <c r="AW7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX7" t="n">
         <v>27</v>
       </c>
       <c r="AY7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ7" t="n">
         <v>2</v>
@@ -1724,7 +1791,7 @@
         <v>16</v>
       </c>
       <c r="BC7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E8" t="n">
         <v>28</v>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H8" t="n">
         <v>48.6</v>
@@ -1771,7 +1838,7 @@
         <v>40.9</v>
       </c>
       <c r="J8" t="n">
-        <v>87</v>
+        <v>86.8</v>
       </c>
       <c r="K8" t="n">
         <v>0.471</v>
@@ -1780,34 +1847,34 @@
         <v>9.5</v>
       </c>
       <c r="M8" t="n">
-        <v>27</v>
+        <v>26.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O8" t="n">
         <v>17.3</v>
       </c>
       <c r="P8" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.761</v>
+        <v>0.762</v>
       </c>
       <c r="R8" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S8" t="n">
-        <v>31.8</v>
+        <v>31.6</v>
       </c>
       <c r="T8" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="U8" t="n">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="V8" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="W8" t="n">
         <v>8</v>
@@ -1816,22 +1883,22 @@
         <v>4.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z8" t="n">
         <v>20.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>108.7</v>
+        <v>108.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AD8" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1843,7 +1910,7 @@
         <v>5</v>
       </c>
       <c r="AH8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1864,19 +1931,19 @@
         <v>13</v>
       </c>
       <c r="AO8" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AP8" t="n">
         <v>19</v>
       </c>
       <c r="AQ8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
         <v>16</v>
       </c>
       <c r="AS8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AT8" t="n">
         <v>17</v>
@@ -1891,7 +1958,7 @@
         <v>11</v>
       </c>
       <c r="AX8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
         <v>3</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-1.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE9" t="n">
         <v>17</v>
@@ -2025,7 +2092,7 @@
         <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI9" t="n">
         <v>13</v>
@@ -2034,7 +2101,7 @@
         <v>4</v>
       </c>
       <c r="AK9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AL9" t="n">
         <v>13</v>
@@ -2064,10 +2131,10 @@
         <v>3</v>
       </c>
       <c r="AU9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AV9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW9" t="n">
         <v>24</v>
@@ -2085,7 +2152,7 @@
         <v>9</v>
       </c>
       <c r="BB9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC9" t="n">
         <v>17</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -2207,10 +2274,10 @@
         <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ10" t="n">
         <v>6</v>
@@ -2231,7 +2298,7 @@
         <v>25</v>
       </c>
       <c r="AP10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ10" t="n">
         <v>29</v>
@@ -2261,7 +2328,7 @@
         <v>17</v>
       </c>
       <c r="AZ10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2477,7 @@
         <v>3</v>
       </c>
       <c r="AO11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP11" t="n">
         <v>22</v>
@@ -2422,7 +2489,7 @@
         <v>24</v>
       </c>
       <c r="AS11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT11" t="n">
         <v>8</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -2481,25 +2548,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F12" t="n">
         <v>13</v>
       </c>
       <c r="G12" t="n">
-        <v>0.675</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
       </c>
       <c r="I12" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J12" t="n">
-        <v>83.5</v>
+        <v>83.3</v>
       </c>
       <c r="K12" t="n">
         <v>0.438</v>
@@ -2508,19 +2575,19 @@
         <v>11.8</v>
       </c>
       <c r="M12" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.35</v>
+        <v>0.352</v>
       </c>
       <c r="O12" t="n">
-        <v>17.3</v>
+        <v>17.7</v>
       </c>
       <c r="P12" t="n">
-        <v>24.2</v>
+        <v>24.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.714</v>
+        <v>0.712</v>
       </c>
       <c r="R12" t="n">
         <v>12.2</v>
@@ -2529,52 +2596,52 @@
         <v>31.2</v>
       </c>
       <c r="T12" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U12" t="n">
         <v>21</v>
       </c>
       <c r="V12" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="W12" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>22.6</v>
+        <v>22.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>20.4</v>
+        <v>20.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>102.3</v>
+        <v>102.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AD12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AF12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ12" t="n">
         <v>16</v>
@@ -2589,25 +2656,25 @@
         <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AP12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
         <v>28</v>
       </c>
       <c r="AR12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS12" t="n">
         <v>22</v>
       </c>
       <c r="AT12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU12" t="n">
         <v>19</v>
@@ -2622,19 +2689,19 @@
         <v>18</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2814,7 @@
         <v>23</v>
       </c>
       <c r="AF13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG13" t="n">
         <v>23</v>
@@ -2759,16 +2826,16 @@
         <v>26</v>
       </c>
       <c r="AJ13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK13" t="n">
         <v>27</v>
       </c>
       <c r="AL13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN13" t="n">
         <v>24</v>
@@ -2786,7 +2853,7 @@
         <v>13</v>
       </c>
       <c r="AS13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT13" t="n">
         <v>4</v>
@@ -2795,7 +2862,7 @@
         <v>20</v>
       </c>
       <c r="AV13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW13" t="n">
         <v>29</v>
@@ -2813,7 +2880,7 @@
         <v>12</v>
       </c>
       <c r="BB13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC13" t="n">
         <v>19</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -2926,13 +2993,13 @@
         <v>5</v>
       </c>
       <c r="AE14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH14" t="n">
         <v>26</v>
@@ -2968,7 +3035,7 @@
         <v>27</v>
       </c>
       <c r="AS14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT14" t="n">
         <v>26</v>
@@ -2995,7 +3062,7 @@
         <v>4</v>
       </c>
       <c r="BB14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC14" t="n">
         <v>4</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -3027,58 +3094,58 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E15" t="n">
         <v>12</v>
       </c>
       <c r="F15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3</v>
+        <v>0.293</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>37.7</v>
+        <v>37.5</v>
       </c>
       <c r="J15" t="n">
-        <v>85.90000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="K15" t="n">
-        <v>0.439</v>
+        <v>0.437</v>
       </c>
       <c r="L15" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M15" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="N15" t="n">
         <v>0.351</v>
       </c>
       <c r="O15" t="n">
-        <v>18.2</v>
+        <v>18.5</v>
       </c>
       <c r="P15" t="n">
-        <v>24.5</v>
+        <v>24.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.744</v>
+        <v>0.746</v>
       </c>
       <c r="R15" t="n">
         <v>11.5</v>
       </c>
       <c r="S15" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="T15" t="n">
-        <v>43.1</v>
+        <v>43</v>
       </c>
       <c r="U15" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V15" t="n">
         <v>12.7</v>
@@ -3087,70 +3154,70 @@
         <v>7.3</v>
       </c>
       <c r="X15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AB15" t="n">
-        <v>100.7</v>
+        <v>100.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.8</v>
+        <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ15" t="n">
         <v>7</v>
       </c>
       <c r="AK15" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AM15" t="n">
         <v>22</v>
       </c>
       <c r="AN15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AP15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AQ15" t="n">
         <v>20</v>
       </c>
       <c r="AR15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AS15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT15" t="n">
         <v>14</v>
@@ -3162,7 +3229,7 @@
         <v>5</v>
       </c>
       <c r="AW15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX15" t="n">
         <v>18</v>
@@ -3171,10 +3238,10 @@
         <v>9</v>
       </c>
       <c r="AZ15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA15" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BB15" t="n">
         <v>17</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>4.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -3305,7 +3372,7 @@
         <v>6</v>
       </c>
       <c r="AJ16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK16" t="n">
         <v>6</v>
@@ -3320,7 +3387,7 @@
         <v>12</v>
       </c>
       <c r="AO16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AP16" t="n">
         <v>13</v>
@@ -3350,19 +3417,19 @@
         <v>22</v>
       </c>
       <c r="AY16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA16" t="n">
         <v>13</v>
       </c>
       <c r="BB16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-3.7</v>
       </c>
       <c r="AD17" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE17" t="n">
         <v>17</v>
@@ -3496,7 +3563,7 @@
         <v>17</v>
       </c>
       <c r="AM17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN17" t="n">
         <v>18</v>
@@ -3505,7 +3572,7 @@
         <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ17" t="n">
         <v>26</v>
@@ -3520,10 +3587,10 @@
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AV17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW17" t="n">
         <v>8</v>
@@ -3538,7 +3605,7 @@
         <v>12</v>
       </c>
       <c r="BA17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
         <v>28</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE18" t="n">
         <v>13</v>
@@ -3666,13 +3733,13 @@
         <v>7</v>
       </c>
       <c r="AI18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ18" t="n">
         <v>24</v>
       </c>
       <c r="AK18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL18" t="n">
         <v>21</v>
@@ -3696,7 +3763,7 @@
         <v>22</v>
       </c>
       <c r="AS18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT18" t="n">
         <v>23</v>
@@ -3714,19 +3781,19 @@
         <v>20</v>
       </c>
       <c r="AY18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ18" t="n">
         <v>27</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
         <v>21</v>
       </c>
       <c r="BC18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-9.199999999999999</v>
       </c>
       <c r="AD19" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE19" t="n">
         <v>29</v>
@@ -3848,13 +3915,13 @@
         <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ19" t="n">
         <v>9</v>
       </c>
       <c r="AK19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL19" t="n">
         <v>30</v>
@@ -3869,7 +3936,7 @@
         <v>7</v>
       </c>
       <c r="AP19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -3952,13 +4019,13 @@
         <v>48.3</v>
       </c>
       <c r="I20" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J20" t="n">
-        <v>83.7</v>
+        <v>84.2</v>
       </c>
       <c r="K20" t="n">
-        <v>0.458</v>
+        <v>0.456</v>
       </c>
       <c r="L20" t="n">
         <v>6.6</v>
@@ -3967,64 +4034,64 @@
         <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.344</v>
+        <v>0.342</v>
       </c>
       <c r="O20" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P20" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.764</v>
+        <v>0.758</v>
       </c>
       <c r="R20" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="S20" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="T20" t="n">
-        <v>43.4</v>
+        <v>43.9</v>
       </c>
       <c r="U20" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V20" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="X20" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.7</v>
+        <v>100.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.2</v>
+        <v>0.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AF20" t="n">
         <v>14</v>
       </c>
       <c r="AG20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH20" t="n">
         <v>21</v>
@@ -4033,37 +4100,37 @@
         <v>11</v>
       </c>
       <c r="AJ20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>25</v>
       </c>
       <c r="AM20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN20" t="n">
         <v>21</v>
       </c>
       <c r="AO20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AR20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AS20" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AU20" t="n">
         <v>15</v>
@@ -4072,16 +4139,16 @@
         <v>7</v>
       </c>
       <c r="AW20" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AX20" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AY20" t="n">
         <v>29</v>
       </c>
       <c r="AZ20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA20" t="n">
         <v>27</v>
@@ -4090,7 +4157,7 @@
         <v>15</v>
       </c>
       <c r="BC20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -4209,7 +4276,7 @@
         <v>30</v>
       </c>
       <c r="AH21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI21" t="n">
         <v>27</v>
@@ -4224,7 +4291,7 @@
         <v>16</v>
       </c>
       <c r="AM21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN21" t="n">
         <v>14</v>
@@ -4254,7 +4321,7 @@
         <v>23</v>
       </c>
       <c r="AW21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -4301,85 +4368,85 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F22" t="n">
         <v>20</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5</v>
+        <v>0.487</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>37.5</v>
+        <v>37.2</v>
       </c>
       <c r="J22" t="n">
         <v>84.3</v>
       </c>
       <c r="K22" t="n">
-        <v>0.444</v>
+        <v>0.441</v>
       </c>
       <c r="L22" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M22" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.327</v>
+        <v>0.326</v>
       </c>
       <c r="O22" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="P22" t="n">
-        <v>24.2</v>
+        <v>24</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.743</v>
+        <v>0.744</v>
       </c>
       <c r="R22" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S22" t="n">
-        <v>34.6</v>
+        <v>34.3</v>
       </c>
       <c r="T22" t="n">
-        <v>46.8</v>
+        <v>46.6</v>
       </c>
       <c r="U22" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="V22" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="W22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="X22" t="n">
         <v>5.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z22" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>100.2</v>
+        <v>99.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AE22" t="n">
         <v>15</v>
@@ -4415,7 +4482,7 @@
         <v>11</v>
       </c>
       <c r="AP22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ22" t="n">
         <v>21</v>
@@ -4424,37 +4491,37 @@
         <v>4</v>
       </c>
       <c r="AS22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
         <v>1</v>
       </c>
       <c r="AU22" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AV22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX22" t="n">
         <v>4</v>
       </c>
       <c r="AY22" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA22" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB22" t="n">
         <v>18</v>
       </c>
       <c r="BC22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -4498,40 +4565,40 @@
         <v>48.1</v>
       </c>
       <c r="I23" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J23" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K23" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L23" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M23" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="N23" t="n">
         <v>0.368</v>
       </c>
       <c r="O23" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="P23" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.731</v>
+        <v>0.73</v>
       </c>
       <c r="R23" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>31.6</v>
+        <v>32</v>
       </c>
       <c r="T23" t="n">
-        <v>40.2</v>
+        <v>40.7</v>
       </c>
       <c r="U23" t="n">
         <v>20.2</v>
@@ -4540,25 +4607,25 @@
         <v>14.7</v>
       </c>
       <c r="W23" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X23" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="Z23" t="n">
         <v>21.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>95.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.5</v>
+        <v>-5.3</v>
       </c>
       <c r="AD23" t="n">
         <v>1</v>
@@ -4570,7 +4637,7 @@
         <v>26</v>
       </c>
       <c r="AG23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AH23" t="n">
         <v>28</v>
@@ -4588,7 +4655,7 @@
         <v>18</v>
       </c>
       <c r="AM23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN23" t="n">
         <v>7</v>
@@ -4597,7 +4664,7 @@
         <v>29</v>
       </c>
       <c r="AP23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ23" t="n">
         <v>27</v>
@@ -4606,13 +4673,13 @@
         <v>28</v>
       </c>
       <c r="AS23" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AT23" t="n">
         <v>28</v>
       </c>
       <c r="AU23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV23" t="n">
         <v>20</v>
@@ -4624,16 +4691,16 @@
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AZ23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-12.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4779,13 +4846,13 @@
         <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ24" t="n">
         <v>30</v>
       </c>
       <c r="AR24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS24" t="n">
         <v>26</v>
@@ -4806,13 +4873,13 @@
         <v>5</v>
       </c>
       <c r="AY24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ24" t="n">
         <v>23</v>
       </c>
       <c r="BA24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -4958,7 +5025,7 @@
         <v>10</v>
       </c>
       <c r="AO25" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP25" t="n">
         <v>23</v>
@@ -4973,19 +5040,19 @@
         <v>19</v>
       </c>
       <c r="AT25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU25" t="n">
         <v>20</v>
       </c>
       <c r="AV25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW25" t="n">
         <v>7</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY25" t="n">
         <v>6</v>
@@ -4997,7 +5064,7 @@
         <v>11</v>
       </c>
       <c r="BB25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC25" t="n">
         <v>11</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -5119,7 +5186,7 @@
         <v>3</v>
       </c>
       <c r="AH26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
         <v>7</v>
@@ -5137,13 +5204,13 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
         <v>27</v>
       </c>
       <c r="AP26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AQ26" t="n">
         <v>2</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-2</v>
       </c>
       <c r="AD27" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AE27" t="n">
         <v>20</v>
@@ -5310,7 +5377,7 @@
         <v>28</v>
       </c>
       <c r="AK27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
@@ -5331,7 +5398,7 @@
         <v>5</v>
       </c>
       <c r="AR27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS27" t="n">
         <v>6</v>
@@ -5361,7 +5428,7 @@
         <v>1</v>
       </c>
       <c r="BB27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC27" t="n">
         <v>21</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -5408,28 +5475,28 @@
         <v>49.1</v>
       </c>
       <c r="I28" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="J28" t="n">
-        <v>83.40000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.46</v>
+        <v>0.463</v>
       </c>
       <c r="L28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="O28" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="P28" t="n">
         <v>22</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.371</v>
-      </c>
-      <c r="O28" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="P28" t="n">
-        <v>22.2</v>
       </c>
       <c r="Q28" t="n">
         <v>0.761</v>
@@ -5438,37 +5505,37 @@
         <v>9.800000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>34.1</v>
+        <v>33.9</v>
       </c>
       <c r="T28" t="n">
-        <v>43.9</v>
+        <v>43.6</v>
       </c>
       <c r="U28" t="n">
         <v>24.6</v>
       </c>
       <c r="V28" t="n">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="W28" t="n">
         <v>7.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="Z28" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB28" t="n">
-        <v>101.8</v>
+        <v>102.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="AD28" t="n">
         <v>5</v>
@@ -5492,19 +5559,19 @@
         <v>17</v>
       </c>
       <c r="AK28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL28" t="n">
         <v>10</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>11</v>
       </c>
       <c r="AM28" t="n">
         <v>15</v>
       </c>
       <c r="AN28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP28" t="n">
         <v>20</v>
@@ -5519,34 +5586,34 @@
         <v>5</v>
       </c>
       <c r="AT28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU28" t="n">
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AW28" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX28" t="n">
         <v>7</v>
       </c>
       <c r="AY28" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA28" t="n">
         <v>22</v>
       </c>
       <c r="BB28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BC28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -5575,94 +5642,94 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E29" t="n">
         <v>26</v>
       </c>
       <c r="F29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29" t="n">
-        <v>0.65</v>
+        <v>0.667</v>
       </c>
       <c r="H29" t="n">
         <v>48.5</v>
       </c>
       <c r="I29" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="J29" t="n">
-        <v>84.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L29" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="M29" t="n">
         <v>25.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0.356</v>
+        <v>0.358</v>
       </c>
       <c r="O29" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P29" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.781</v>
+        <v>0.779</v>
       </c>
       <c r="R29" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S29" t="n">
         <v>30.5</v>
       </c>
       <c r="T29" t="n">
-        <v>41.7</v>
+        <v>41.8</v>
       </c>
       <c r="U29" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V29" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="W29" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X29" t="n">
         <v>4.4</v>
       </c>
       <c r="Y29" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AA29" t="n">
         <v>21.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>106.8</v>
+        <v>107.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AE29" t="n">
         <v>10</v>
       </c>
       <c r="AF29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG29" t="n">
         <v>8</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>9</v>
       </c>
       <c r="AH29" t="n">
         <v>11</v>
@@ -5671,10 +5738,10 @@
         <v>5</v>
       </c>
       <c r="AJ29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL29" t="n">
         <v>8</v>
@@ -5689,13 +5756,13 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ29" t="n">
         <v>3</v>
       </c>
       <c r="AR29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS29" t="n">
         <v>25</v>
@@ -5704,13 +5771,13 @@
         <v>22</v>
       </c>
       <c r="AU29" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AV29" t="n">
         <v>4</v>
       </c>
       <c r="AW29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX29" t="n">
         <v>21</v>
@@ -5719,13 +5786,13 @@
         <v>19</v>
       </c>
       <c r="AZ29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA29" t="n">
         <v>5</v>
       </c>
       <c r="BB29" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BC29" t="n">
         <v>6</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -5757,85 +5824,85 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E30" t="n">
         <v>14</v>
       </c>
       <c r="F30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G30" t="n">
-        <v>0.341</v>
+        <v>0.35</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>35.6</v>
+        <v>35.8</v>
       </c>
       <c r="J30" t="n">
-        <v>79</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.451</v>
+        <v>0.454</v>
       </c>
       <c r="L30" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M30" t="n">
-        <v>20.6</v>
+        <v>20.8</v>
       </c>
       <c r="N30" t="n">
         <v>0.335</v>
       </c>
       <c r="O30" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="P30" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.75</v>
+        <v>0.752</v>
       </c>
       <c r="R30" t="n">
         <v>11.5</v>
       </c>
       <c r="S30" t="n">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="T30" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U30" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="V30" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W30" t="n">
         <v>6.7</v>
       </c>
       <c r="X30" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z30" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>19.4</v>
+        <v>19.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>95.5</v>
+        <v>96.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>-3.4</v>
+        <v>-3</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="AE30" t="n">
         <v>25</v>
@@ -5844,7 +5911,7 @@
         <v>24</v>
       </c>
       <c r="AG30" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AH30" t="n">
         <v>29</v>
@@ -5856,19 +5923,19 @@
         <v>29</v>
       </c>
       <c r="AK30" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AL30" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AM30" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AN30" t="n">
         <v>23</v>
       </c>
       <c r="AO30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP30" t="n">
         <v>15</v>
@@ -5877,16 +5944,16 @@
         <v>17</v>
       </c>
       <c r="AR30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT30" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV30" t="n">
         <v>24</v>
@@ -5895,10 +5962,10 @@
         <v>25</v>
       </c>
       <c r="AX30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AY30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ30" t="n">
         <v>5</v>
@@ -5907,7 +5974,7 @@
         <v>24</v>
       </c>
       <c r="BB30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC30" t="n">
         <v>24</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
@@ -6023,13 +6090,13 @@
         <v>5</v>
       </c>
       <c r="AF31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI31" t="n">
         <v>9</v>
@@ -6065,7 +6132,7 @@
         <v>12</v>
       </c>
       <c r="AT31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU31" t="n">
         <v>4</v>
@@ -6086,7 +6153,7 @@
         <v>18</v>
       </c>
       <c r="BA31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB31" t="n">
         <v>19</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-18-2014-15</t>
+          <t>2015-01-18</t>
         </is>
       </c>
     </row>
